--- a/business_forms/031_material_count_survey--business_forms.xlsx
+++ b/business_forms/031_material_count_survey--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,13 +525,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>material_count</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is the total count of materials?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please provide the total count of materials.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,13 +552,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>material_type</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>What type of material are we counting?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Select all that apply.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,13 +579,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>count_of_materials</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>What is the count of materials of this type?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please provide the count of materials.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,20 +606,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>material_count_survey_5</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Is this material count correct?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Yes or No.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,82 +633,98 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>material_count_survey_6</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Is this material type correct?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Yes or No.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>material_count_survey_7</t>
+          <t>material_count_survey_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>material_count</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>What is the quantity of materials?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please provide the quantity of materials.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>material_count_survey_8</t>
+          <t>material_count_survey_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>material_type</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>What is the count of materials?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please provide the count of materials.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>material_count_survey_9</t>
+          <t>material_count_survey_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>quantity_of_materials</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Do we have this material type?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Yes or No.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,39 +736,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>material_count_survey_9</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>material_count_survey_10</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>count_of_materials</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>material_count_survey_11</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>material_type</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -753,10 +762,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
@@ -905,12 +914,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>one</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>One</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -922,163 +931,78 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>two</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Two</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>material_count_survey_4_choices</t>
+          <t>material_count_survey_5_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>three</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Three</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>material_count_survey_4_choices</t>
+          <t>material_count_survey_5_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>four</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Four</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>material_count_survey_4_choices</t>
+          <t>material_count_survey_8_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>five</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Five</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>material_count_survey_7_choices</t>
+          <t>material_count_survey_8_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>material_count_survey_7_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>material_count_survey_8_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>material_count_survey_8_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>material_count_survey_11_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>material_count_survey_11_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
         <is>
           <t>No</t>
         </is>
